--- a/emails.xlsx
+++ b/emails.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmed/Desktop/Emailscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CCBF17-BF5F-7543-A529-F54BB33BA207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB67F63-9F92-134A-B7B6-4A5AB036DA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14680" yWindow="680" windowWidth="14720" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Emails" sheetId="1" r:id="rId1"/>
@@ -20,34 +20,1195 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="394">
   <si>
     <t>email</t>
   </si>
   <si>
-    <t>aa.ah201222@gmail.com</t>
-  </si>
-  <si>
-    <t>xfateen1@gmail.com</t>
-  </si>
-  <si>
-    <t>a.alhrbi2001@gmail.com</t>
-  </si>
-  <si>
-    <t>iiiksasa15@gmail.com</t>
-  </si>
-  <si>
-    <t>ahmed20001dev@gmail.com</t>
-  </si>
-  <si>
-    <t>ahmed2024dev@gmail.com</t>
+    <t>Recruitment@aaw.com.sa</t>
+  </si>
+  <si>
+    <t>solaiman@sak-consult.com</t>
+  </si>
+  <si>
+    <t>info@tya-sa.com</t>
+  </si>
+  <si>
+    <t>mshkara@zfp.com</t>
+  </si>
+  <si>
+    <t>hebshi923@yahoo.com</t>
+  </si>
+  <si>
+    <t>salem@rawasi.com.sa</t>
+  </si>
+  <si>
+    <t>Riyadh@khatibalami.com</t>
+  </si>
+  <si>
+    <t>hanialonaizy@safari.com.sa</t>
+  </si>
+  <si>
+    <t>gmoffice@ssem.com.sa</t>
+  </si>
+  <si>
+    <t>adel@altoukhi.com</t>
+  </si>
+  <si>
+    <t>mabdulwahab@rtcc.com.sa</t>
+  </si>
+  <si>
+    <t>Amjad.Abed-Alhakim@alfanar.com</t>
+  </si>
+  <si>
+    <t>m.alzughaibi@alsayedgroup.com</t>
+  </si>
+  <si>
+    <t>hbelbeisi@alfouzan.com</t>
+  </si>
+  <si>
+    <t>a.alballaa@arail.com.sa</t>
+  </si>
+  <si>
+    <t>bdargmeh@femco.com.sa</t>
+  </si>
+  <si>
+    <t>saud@el-seif.com.sa</t>
+  </si>
+  <si>
+    <t>aalbanyan@yuksel.net</t>
+  </si>
+  <si>
+    <t>ashraf.hassaan@arrab.com.sa</t>
+  </si>
+  <si>
+    <t>info@nwwc.com.sa</t>
+  </si>
+  <si>
+    <t>info@alasila.com</t>
+  </si>
+  <si>
+    <t>emad.lasheen@ymco.sa</t>
+  </si>
+  <si>
+    <t>abdullah.alshahrani@gulfgroupco.com</t>
+  </si>
+  <si>
+    <t>admin@atsc-sa.com</t>
+  </si>
+  <si>
+    <t>info@etechsco.com</t>
+  </si>
+  <si>
+    <t>mohamedwagdy1980@yahoo.com</t>
+  </si>
+  <si>
+    <t>info@jawdat.com.sa</t>
+  </si>
+  <si>
+    <t>fahad.almangour@abvrock.com</t>
+  </si>
+  <si>
+    <t>painzain0@gmail.com</t>
+  </si>
+  <si>
+    <t>alaa.alkhamees@latifia.com</t>
+  </si>
+  <si>
+    <t>mostafa@tech-develop.com</t>
+  </si>
+  <si>
+    <t>mohd_ragab@al-mohtaseb.com</t>
+  </si>
+  <si>
+    <t>saad_h@alawadgroup.com</t>
+  </si>
+  <si>
+    <t>ralsuhaibani@horizon.sa</t>
+  </si>
+  <si>
+    <t>Masco@masco.com.sa</t>
+  </si>
+  <si>
+    <t>nawaf@abc.sa.com</t>
+  </si>
+  <si>
+    <t>talsayadi@alkhorayef.com</t>
+  </si>
+  <si>
+    <t>acc.almolhaq@outlook.sa</t>
+  </si>
+  <si>
+    <t>farouk.badr@buildingtek.com</t>
+  </si>
+  <si>
+    <t>saad.anaze@sapac.com.sa</t>
+  </si>
+  <si>
+    <t>ahmed.helmy@wadimaramer.net</t>
+  </si>
+  <si>
+    <t>faifi@sedergroup.com</t>
+  </si>
+  <si>
+    <t>nakity@snscl.com</t>
+  </si>
+  <si>
+    <t>nashwan.alsalmy@almobty.com</t>
+  </si>
+  <si>
+    <t>sultan.almurshed@daralriyadh.com</t>
+  </si>
+  <si>
+    <t>s.suhaib@timnatelecoms.com</t>
+  </si>
+  <si>
+    <t>mirghanieissa@hotmail.com</t>
+  </si>
+  <si>
+    <t>abdullah.alturaiki@ccesaudi.com</t>
+  </si>
+  <si>
+    <t>intermaint2015@gmail.com</t>
+  </si>
+  <si>
+    <t>salahmustafa@metco-sa.com</t>
+  </si>
+  <si>
+    <t>srahem@mag-sa.com</t>
+  </si>
+  <si>
+    <t>office@taktheer.net</t>
+  </si>
+  <si>
+    <t>s8007000@hotmail.com</t>
+  </si>
+  <si>
+    <t>nazem.nazzal@arrab.com.sa</t>
+  </si>
+  <si>
+    <t>acc-hesham@sdn.com.sa</t>
+  </si>
+  <si>
+    <t>t.pacha@midgrkl.com</t>
+  </si>
+  <si>
+    <t>bahaa.anwer@algihaz.com</t>
+  </si>
+  <si>
+    <t>razzam@unitedccc.com</t>
+  </si>
+  <si>
+    <t>info@saad-construction.com</t>
+  </si>
+  <si>
+    <t>info@zahrang.com</t>
+  </si>
+  <si>
+    <t>alabody123123123@gmail.com</t>
+  </si>
+  <si>
+    <t>s.sabra@zaidg.com</t>
+  </si>
+  <si>
+    <t>ayman@alrosan.com.sa</t>
+  </si>
+  <si>
+    <t>Nasserjalil@asoc.com.sa</t>
+  </si>
+  <si>
+    <t>info@arbrock.com</t>
+  </si>
+  <si>
+    <t>hegazey@azizcompany.com</t>
+  </si>
+  <si>
+    <t>artec_com@yahoo.com</t>
+  </si>
+  <si>
+    <t>ahmed.qashoa@mrtc.com.sa</t>
+  </si>
+  <si>
+    <t>info@hashem-contracting.com</t>
+  </si>
+  <si>
+    <t>FAHAD.ALJASSER@SCDCO.SA</t>
+  </si>
+  <si>
+    <t>clc967@gmail.com</t>
+  </si>
+  <si>
+    <t>mesh5al1500@gmail.com</t>
+  </si>
+  <si>
+    <t>loom321@gmail.com</t>
+  </si>
+  <si>
+    <t>hrfirstsaudi@gmail.com</t>
+  </si>
+  <si>
+    <t>bosalman60@yahoo.com</t>
+  </si>
+  <si>
+    <t>mmohsen@manwasa.com</t>
+  </si>
+  <si>
+    <t>bae-1980@hotmail.com</t>
+  </si>
+  <si>
+    <t>hamdi@jaroudigroup.com</t>
+  </si>
+  <si>
+    <t>m7_mb@hotmail.com</t>
+  </si>
+  <si>
+    <t>info@acco.sa</t>
+  </si>
+  <si>
+    <t>info@mpf.almarshad.com</t>
+  </si>
+  <si>
+    <t>sultan@algadeibi.com</t>
+  </si>
+  <si>
+    <t>info@tojar.com.sa</t>
+  </si>
+  <si>
+    <t>aalshehri@samama.com</t>
+  </si>
+  <si>
+    <t>alkhateeb@alkhateeb.com.sa</t>
+  </si>
+  <si>
+    <t>ceo@sicep.com</t>
+  </si>
+  <si>
+    <t>abdulkhalig@mashail.com.sa</t>
+  </si>
+  <si>
+    <t>classification@alayuni.com</t>
+  </si>
+  <si>
+    <t>ahmad@raissy.com.sa</t>
+  </si>
+  <si>
+    <t>info@mgc.com.sa</t>
+  </si>
+  <si>
+    <t>mohamad@alwareef.com.sa</t>
+  </si>
+  <si>
+    <t>eelmasry@daralbena.com</t>
+  </si>
+  <si>
+    <t>info@alrajhi-co.sa</t>
+  </si>
+  <si>
+    <t>mohamed.a@alothman-gp.com</t>
+  </si>
+  <si>
+    <t>CV@Arabianfal.com</t>
+  </si>
+  <si>
+    <t>Cv@aldawaa.com.sa</t>
+  </si>
+  <si>
+    <t>Hr.qrm@hotmail.com</t>
+  </si>
+  <si>
+    <t>Rec@alojaimi.com</t>
+  </si>
+  <si>
+    <t>Recruitment@rawabiholding.com</t>
+  </si>
+  <si>
+    <t>Job.s6@hotmail.com</t>
+  </si>
+  <si>
+    <t>Careers@dnata.com</t>
+  </si>
+  <si>
+    <t>Hr@alesayi_motors.com</t>
+  </si>
+  <si>
+    <t>Hr@alarayan.com</t>
+  </si>
+  <si>
+    <t>Recruiting.ksa@mcmermott.com</t>
+  </si>
+  <si>
+    <t>Recruitment@aytb.com</t>
+  </si>
+  <si>
+    <t>Wadaef@gtecorp.com</t>
+  </si>
+  <si>
+    <t>Careers@nesr.com</t>
+  </si>
+  <si>
+    <t>Recruit@farm.com.sa</t>
+  </si>
+  <si>
+    <t>Info@alhumamlaw.com</t>
+  </si>
+  <si>
+    <t>Hr1@gulfteksaudi.com</t>
+  </si>
+  <si>
+    <t>Catcosa@catcosa.com</t>
+  </si>
+  <si>
+    <t>Cv@tafear.com</t>
+  </si>
+  <si>
+    <t>Recruitment@sraco.com.sa</t>
+  </si>
+  <si>
+    <t>Career@sidco.com.sa</t>
+  </si>
+  <si>
+    <t>Info@atco.com.sa</t>
+  </si>
+  <si>
+    <t>HRdepartmental@sa.yokogawa.com</t>
+  </si>
+  <si>
+    <t>Recruitment@shadeco.com</t>
+  </si>
+  <si>
+    <t>Klc.hr@alkafaa.com</t>
+  </si>
+  <si>
+    <t>Kbr-amcdehr@kbr.com</t>
+  </si>
+  <si>
+    <t>Recruitment@batook.com</t>
+  </si>
+  <si>
+    <t>Career@shawarmer.com</t>
+  </si>
+  <si>
+    <t>Hrsupport@archirodon.net</t>
+  </si>
+  <si>
+    <t>Jobs@binajinah.com</t>
+  </si>
+  <si>
+    <t>Marketing.np@nesma.com</t>
+  </si>
+  <si>
+    <t>Wadaef2019@abdulla-fouad.com</t>
+  </si>
+  <si>
+    <t>Careers@innosoft.sa</t>
+  </si>
+  <si>
+    <t>M@startime.com.sa</t>
+  </si>
+  <si>
+    <t>job@musk.sa.com</t>
+  </si>
+  <si>
+    <t>Shababwatansa@gmail.com</t>
+  </si>
+  <si>
+    <t>j@sabksa.com</t>
+  </si>
+  <si>
+    <t>al.alshaikh@bonyan.sa</t>
+  </si>
+  <si>
+    <t>ymohammed@innovest.com.sa</t>
+  </si>
+  <si>
+    <t>s.alwadi@nhc.sa</t>
+  </si>
+  <si>
+    <t>i.atassi@artar.com.sa</t>
+  </si>
+  <si>
+    <t>oalkhunaizi@darwaemaar.com</t>
+  </si>
+  <si>
+    <t>jobs@almasah.net</t>
+  </si>
+  <si>
+    <t>recruitment.amjad@gmail.com</t>
+  </si>
+  <si>
+    <t>jobrydlaw@gmail.com</t>
+  </si>
+  <si>
+    <t>Job@almoosahospital.com.sa</t>
+  </si>
+  <si>
+    <t>recruitment@almoosahospital.com.sa</t>
+  </si>
+  <si>
+    <t>jobs@sghgroup.net</t>
+  </si>
+  <si>
+    <t>career.dmm@sghgroup.net</t>
+  </si>
+  <si>
+    <t>talent.acquisition@drsulaimanalhabib.com</t>
+  </si>
+  <si>
+    <t>Careers@jhah.com</t>
+  </si>
+  <si>
+    <t>hrd@alahsahospital.com.sa</t>
+  </si>
+  <si>
+    <t>career@almanahospital.com.sa</t>
+  </si>
+  <si>
+    <t>info@familycare.com.sa</t>
+  </si>
+  <si>
+    <t>info@ramclinics.com</t>
+  </si>
+  <si>
+    <t>HR.DSFHR@fakeeh.care</t>
+  </si>
+  <si>
+    <t>career@mouwasat.com</t>
+  </si>
+  <si>
+    <t>careers@dallah-hospital.com</t>
+  </si>
+  <si>
+    <t>hr.phc@drsulaimanalhabib.com</t>
+  </si>
+  <si>
+    <t>careers@almurjanhospital.com</t>
+  </si>
+  <si>
+    <t>hiringnow.ksa@gmail.com</t>
+  </si>
+  <si>
+    <t>recruitment@wecareksa.com</t>
+  </si>
+  <si>
+    <t>info@mofarrehalharbi.com</t>
+  </si>
+  <si>
+    <t>info@nesma-partners.com</t>
+  </si>
+  <si>
+    <t>info@alyamama.com</t>
+  </si>
+  <si>
+    <t>info@al-ayuni.com</t>
+  </si>
+  <si>
+    <t>info@transkingdom-sapac.com</t>
+  </si>
+  <si>
+    <t>info@al-barrak.com</t>
+  </si>
+  <si>
+    <t>info@tamimi.com</t>
+  </si>
+  <si>
+    <t>info@fmsco.com</t>
+  </si>
+  <si>
+    <t>info@aramaram.com</t>
+  </si>
+  <si>
+    <t>info@al-shalawi-holding.com</t>
+  </si>
+  <si>
+    <t>info@powerchina.com</t>
+  </si>
+  <si>
+    <t>info@mobco.com</t>
+  </si>
+  <si>
+    <t>info@elseef.com</t>
+  </si>
+  <si>
+    <t>info@almabani.com</t>
+  </si>
+  <si>
+    <t>info@al-osais.com</t>
+  </si>
+  <si>
+    <t>ghada.asmar@nesma.com</t>
+  </si>
+  <si>
+    <t>m.mhariri@makkiyoon.com</t>
+  </si>
+  <si>
+    <t>suliman@shar.com.sa</t>
+  </si>
+  <si>
+    <t>hiefa@salmansaedan.com</t>
+  </si>
+  <si>
+    <t>s.albatli@ladun.sa</t>
+  </si>
+  <si>
+    <t>gm@leenammar.com</t>
+  </si>
+  <si>
+    <t>alforaihb@al-mozaini.com</t>
+  </si>
+  <si>
+    <t>turki@alfaf.com.sa</t>
+  </si>
+  <si>
+    <t>sami.alzakri@maskanarabia.com</t>
+  </si>
+  <si>
+    <t>a.albarrak@gulfrdc.com</t>
+  </si>
+  <si>
+    <t>gr@alarkan.co</t>
+  </si>
+  <si>
+    <t>m.almutawa@madinatalwouroud.com</t>
+  </si>
+  <si>
+    <t>aali@sac.com.sa</t>
+  </si>
+  <si>
+    <t>marouan@alfahd.com</t>
+  </si>
+  <si>
+    <t>taldubaikhi@al-tahaluf.com</t>
+  </si>
+  <si>
+    <t>ssaedan@al-tahaluf.com</t>
+  </si>
+  <si>
+    <t>info@thakher.com.sa</t>
+  </si>
+  <si>
+    <t>bandaraldheek@anan.com.sa</t>
+  </si>
+  <si>
+    <t>Abdulellahh@rafal.com.sa</t>
+  </si>
+  <si>
+    <t>abdullah@alzamel-realestate.com</t>
+  </si>
+  <si>
+    <t>algamedy@sadeenarabia.com</t>
+  </si>
+  <si>
+    <t>a.ghamdi@sondos.com.sa</t>
+  </si>
+  <si>
+    <t>hanyosman@daajan.com</t>
+  </si>
+  <si>
+    <t>u.shahatah@jdurc.com</t>
+  </si>
+  <si>
+    <t>n.alhammad@jadaara.com.sa</t>
+  </si>
+  <si>
+    <t>alishar@alishar.com</t>
+  </si>
+  <si>
+    <t>ceo@alwkeelgroup.com</t>
+  </si>
+  <si>
+    <t>aziz.aladwan@gmail.com</t>
+  </si>
+  <si>
+    <t>a.almuzaini@sateaa.com</t>
+  </si>
+  <si>
+    <t>abdulaziz@almousaco.com</t>
+  </si>
+  <si>
+    <t>naif@aldyar.sa</t>
+  </si>
+  <si>
+    <t>mmetwaly@abrcontracting.com</t>
+  </si>
+  <si>
+    <t>afayez@samama.com</t>
+  </si>
+  <si>
+    <t>ksasa15@hotmail.com</t>
+  </si>
+  <si>
+    <t>sales.d2@zulfi-sa.com</t>
+  </si>
+  <si>
+    <t>info@gisf.com.sa</t>
+  </si>
+  <si>
+    <t>1U5SR.Ashaduzzaman@alruqee.com</t>
+  </si>
+  <si>
+    <t>imad.hadwan@mmm.com</t>
+  </si>
+  <si>
+    <t>m.rasras@sghcl.com</t>
+  </si>
+  <si>
+    <t>raymond@zamilcd.com.sa</t>
+  </si>
+  <si>
+    <t>sales.alamgir@mctgroups.com</t>
+  </si>
+  <si>
+    <t>material@sources.com</t>
+  </si>
+  <si>
+    <t>naseem@er.ahg.com.sa</t>
+  </si>
+  <si>
+    <t>moktrading@hotmail.com</t>
+  </si>
+  <si>
+    <t>ashar@cesco-omron.com</t>
+  </si>
+  <si>
+    <t>alain.saade@jas.com</t>
+  </si>
+  <si>
+    <t>jsunshinesa@gmail.com</t>
+  </si>
+  <si>
+    <t>imran@sabahtech.com</t>
+  </si>
+  <si>
+    <t>charbeljarjour@icjubail.com.sa</t>
+  </si>
+  <si>
+    <t>khan@immh.co</t>
+  </si>
+  <si>
+    <t>info@assawayer.com/palaksha@assawayer.com</t>
+  </si>
+  <si>
+    <t>manoj.kumar@almojilservices.com</t>
+  </si>
+  <si>
+    <t>info@miesteel.com</t>
+  </si>
+  <si>
+    <t>sales.jubail@alkhodartravel.com</t>
+  </si>
+  <si>
+    <t>1ucsr.Ashaduzzaman@alruqee.com</t>
+  </si>
+  <si>
+    <t>info@aladwanigroup.com</t>
+  </si>
+  <si>
+    <t>trezk@elajougroup.com</t>
+  </si>
+  <si>
+    <t>maraicar.s@worklogixme.com</t>
+  </si>
+  <si>
+    <t>ksbiju@rashidaldossary.com</t>
+  </si>
+  <si>
+    <t>info@inmaajubail.com</t>
+  </si>
+  <si>
+    <t>alg@alf-fouzangroup.com</t>
+  </si>
+  <si>
+    <t>masudcac@gmail.com</t>
+  </si>
+  <si>
+    <t>usman@aladwanigroup.com</t>
+  </si>
+  <si>
+    <t>asif.malik@nabharubber.com</t>
+  </si>
+  <si>
+    <t>a.hajiri@developmentsources.org</t>
+  </si>
+  <si>
+    <t>1u4sales.Azeemuddin@alruqee.com</t>
+  </si>
+  <si>
+    <t>hadi_alajmi2013@yahoo.com</t>
+  </si>
+  <si>
+    <t>abdulrahman.aggad@inmatrading.com.sa</t>
+  </si>
+  <si>
+    <t>info@altamayz.com</t>
+  </si>
+  <si>
+    <t>info@hatcogroups.com</t>
+  </si>
+  <si>
+    <t>ibashir@sahara.com</t>
+  </si>
+  <si>
+    <t>aee_jubail@arabequipmentest.com</t>
+  </si>
+  <si>
+    <t>rgupta@idexcorp.com</t>
+  </si>
+  <si>
+    <t>fahadtnr@aloctg.com</t>
+  </si>
+  <si>
+    <t>info@makana.com.sa</t>
+  </si>
+  <si>
+    <t>omer@advancemachinery.com.sa</t>
+  </si>
+  <si>
+    <t>planning@algaswa.com</t>
+  </si>
+  <si>
+    <t>info@altamyaz.com</t>
+  </si>
+  <si>
+    <t>almhannaacostruction@gmail.com</t>
+  </si>
+  <si>
+    <t>abhilash@jbg.sa.com</t>
+  </si>
+  <si>
+    <t>allafinri@yahoo.com</t>
+  </si>
+  <si>
+    <t>tharwt_saudirod@yahoo.com</t>
+  </si>
+  <si>
+    <t>arshad@qurumtech.com</t>
+  </si>
+  <si>
+    <t>rhejubail@jeraisy.com</t>
+  </si>
+  <si>
+    <t>16HMA.Aftab@alruqee.com</t>
+  </si>
+  <si>
+    <t>emetals@alfozan.com</t>
+  </si>
+  <si>
+    <t>sashidharan1949@yahoo.com</t>
+  </si>
+  <si>
+    <t>tshanavas@aaltaher.com</t>
+  </si>
+  <si>
+    <t>jamal@firetechksa.com</t>
+  </si>
+  <si>
+    <t>sreekanth.p@pressuresystemsksa.com</t>
+  </si>
+  <si>
+    <t>creditcontrol.Ashaduzzaman@alruqee.com</t>
+  </si>
+  <si>
+    <t>majid@arabianlojam.com</t>
+  </si>
+  <si>
+    <t>craneservices@smart.arabian.com</t>
+  </si>
+  <si>
+    <t>burgeon.it@gmail.com</t>
+  </si>
+  <si>
+    <t>alshakra-hassnain@hotmail.com</t>
+  </si>
+  <si>
+    <t>ameen_aso@yahoo.com</t>
+  </si>
+  <si>
+    <t>ialmulla@emc.com.sa</t>
+  </si>
+  <si>
+    <t>burpowerliftersa.comhan@</t>
+  </si>
+  <si>
+    <t>kashif.masood@arabianetimaad.com</t>
+  </si>
+  <si>
+    <t>zakir.rental@gmail.com</t>
+  </si>
+  <si>
+    <t>dawood@silverlineassociates.com</t>
+  </si>
+  <si>
+    <t>ac@bdrdm.com</t>
+  </si>
+  <si>
+    <t>teamlifting@gmail.com</t>
+  </si>
+  <si>
+    <t>jhun.ts@gulfchanels.com</t>
+  </si>
+  <si>
+    <t>ismail.alalwan@gmail.com</t>
+  </si>
+  <si>
+    <t>omprakash@pangulfws.com</t>
+  </si>
+  <si>
+    <t>siddique@hicksa.com</t>
+  </si>
+  <si>
+    <t>munazzah.shariq@alkhodari.com</t>
+  </si>
+  <si>
+    <t>nathaniel@intecc.co</t>
+  </si>
+  <si>
+    <t>threedimension1@yahoo.com</t>
+  </si>
+  <si>
+    <t>kkumar@supportarabia.com</t>
+  </si>
+  <si>
+    <t>rajan@misarabia.com.sa</t>
+  </si>
+  <si>
+    <t>townhardware@gmail.com</t>
+  </si>
+  <si>
+    <t>sales@sharpgt.com</t>
+  </si>
+  <si>
+    <t>ahmed.ahmed@aramex.com</t>
+  </si>
+  <si>
+    <t>john@misarabia.com.sa</t>
+  </si>
+  <si>
+    <t>vasanth@ferrograte.com</t>
+  </si>
+  <si>
+    <t>reemtrading12@yahoo.com</t>
+  </si>
+  <si>
+    <t>info@rkest.com</t>
+  </si>
+  <si>
+    <t>hithesh@mister-machine.com</t>
+  </si>
+  <si>
+    <t>njm.sah@gmail.com</t>
+  </si>
+  <si>
+    <t>merajnafco.jnsf@gmail.com</t>
+  </si>
+  <si>
+    <t>jbsales@sste.sa.com</t>
+  </si>
+  <si>
+    <t>gamarabiasm@gmail.com</t>
+  </si>
+  <si>
+    <t>afsal@dayalsteelonline.com</t>
+  </si>
+  <si>
+    <t>akif@dli-it.com</t>
+  </si>
+  <si>
+    <t>zhmalik20710@gmail.com</t>
+  </si>
+  <si>
+    <t>shameer@scomsys.com</t>
+  </si>
+  <si>
+    <t>4E2CSR.JOSE@alruqee.com</t>
+  </si>
+  <si>
+    <t>aliabdel@univest,com.sa</t>
+  </si>
+  <si>
+    <t>CONTACT@SAUINTGROUP.COM</t>
+  </si>
+  <si>
+    <t>wabduljabbar@alkhorayef.com</t>
+  </si>
+  <si>
+    <t>info@jag.com.sa</t>
+  </si>
+  <si>
+    <t>asmahamood@gmail.com</t>
+  </si>
+  <si>
+    <t>alwaha-ksa@hotmail.com</t>
+  </si>
+  <si>
+    <t>faisal@gisf.com.sa</t>
+  </si>
+  <si>
+    <t>sales.ati@ati-gulf.com</t>
+  </si>
+  <si>
+    <t>mubin@psime.com</t>
+  </si>
+  <si>
+    <t>1U5CSR.Ashaduzzaman</t>
+  </si>
+  <si>
+    <t>intekhab@hhaulers.com</t>
+  </si>
+  <si>
+    <t>mansoor0501193790@gmail.com</t>
+  </si>
+  <si>
+    <t>iqbal@anseglobal.com</t>
+  </si>
+  <si>
+    <t>sales-saudi@vineyardgroup.net</t>
+  </si>
+  <si>
+    <t>shibith@aladwanigroup.com</t>
+  </si>
+  <si>
+    <t>sales@fatehaljubail.com</t>
+  </si>
+  <si>
+    <t>mke@technotogroup.com</t>
+  </si>
+  <si>
+    <t>sajad@madeenapvc.com</t>
+  </si>
+  <si>
+    <t>jubail@namat.com</t>
+  </si>
+  <si>
+    <t>jubaillshrm@mejdaf.com</t>
+  </si>
+  <si>
+    <t>info@alshamranigroup.com</t>
+  </si>
+  <si>
+    <t>geogrid@latifia.com</t>
+  </si>
+  <si>
+    <t>fabco@salembathamer.com</t>
+  </si>
+  <si>
+    <t>taha@aktesa.com</t>
+  </si>
+  <si>
+    <t>mohammed.elshaarawy@el-sewedy.com</t>
+  </si>
+  <si>
+    <t>ros5753322@hotmail.com</t>
+  </si>
+  <si>
+    <t>haitham@almousasacables.com</t>
+  </si>
+  <si>
+    <t>hadippress@yahoo.com</t>
+  </si>
+  <si>
+    <t>omarna@akh.com.sa</t>
+  </si>
+  <si>
+    <t>info@eaglehydraulicservice.com</t>
+  </si>
+  <si>
+    <t>koshy@khamisainhardware.com</t>
+  </si>
+  <si>
+    <t>info@saudithalate.com</t>
+  </si>
+  <si>
+    <t>sales@hindasent.com</t>
+  </si>
+  <si>
+    <t>sheikh_ngc@yahoo.com</t>
+  </si>
+  <si>
+    <t>liyaqat_m@yahoo.com</t>
+  </si>
+  <si>
+    <t>hertz@alkhodari.com</t>
+  </si>
+  <si>
+    <t>mha_mangalore@yahoo.com</t>
+  </si>
+  <si>
+    <t>sukeshcrystal@yahoo.com</t>
+  </si>
+  <si>
+    <t>samaajubail@gmail.com</t>
+  </si>
+  <si>
+    <t>info@superior.com.sa</t>
+  </si>
+  <si>
+    <t>info@enzonme.com</t>
+  </si>
+  <si>
+    <t>mbmjubail@yahoo.com</t>
+  </si>
+  <si>
+    <t>ith@ithest.net</t>
+  </si>
+  <si>
+    <t>pillai_us1@yahoo.com</t>
+  </si>
+  <si>
+    <t>dastagir@cmci-sa.com</t>
+  </si>
+  <si>
+    <t>fiazsiddique@yahoo.com</t>
+  </si>
+  <si>
+    <t>sales@alhodaco.com</t>
+  </si>
+  <si>
+    <t>info@atc.sa.com</t>
+  </si>
+  <si>
+    <t>daniel.thomson@worleypersons.com</t>
+  </si>
+  <si>
+    <t>salim.moideen@aramco.com</t>
+  </si>
+  <si>
+    <t>khaled-thiab@yahoo.com</t>
+  </si>
+  <si>
+    <t>#J-R-G-C@Hotmail.com</t>
+  </si>
+  <si>
+    <t>bijisnairamasco@gmail.com</t>
+  </si>
+  <si>
+    <t>sufyan@sste,sa.com</t>
+  </si>
+  <si>
+    <t>az_mod2009@yahoo.com</t>
+  </si>
+  <si>
+    <t>ajmi-130@hotmail.com</t>
+  </si>
+  <si>
+    <t>fahad.mic@gmail.com</t>
+  </si>
+  <si>
+    <t>contracts@alliedtechsa.com</t>
+  </si>
+  <si>
+    <t>biju@southemrock.com.sa</t>
+  </si>
+  <si>
+    <t>shajik@awtads.com</t>
+  </si>
+  <si>
+    <t>mki_akhas@yahoo.com</t>
+  </si>
+  <si>
+    <t>eliteinvention@gmail.com</t>
+  </si>
+  <si>
+    <t>zaki_dksc@yahoo.com</t>
+  </si>
+  <si>
+    <t>johir_kondaker@yahoo.com</t>
+  </si>
+  <si>
+    <t>amamon@gulfconnectsa.com</t>
+  </si>
+  <si>
+    <t>alm_almgir@yahoo.com</t>
+  </si>
+  <si>
+    <t>unitedaseel@gmail.com</t>
+  </si>
+  <si>
+    <t>raslkhaleej2020@yahoo.com</t>
+  </si>
+  <si>
+    <t>navasteejan@gmail.com</t>
+  </si>
+  <si>
+    <t>fahad_khalid01@yahoo.com</t>
+  </si>
+  <si>
+    <t>mujibkavitvr@yahoo.co.in</t>
+  </si>
+  <si>
+    <t>msquarebabu_mrb@yahoo.com</t>
+  </si>
+  <si>
+    <t>mahacodmm@yahoo.com</t>
+  </si>
+  <si>
+    <t>jsgce2009@yahoo.com</t>
+  </si>
+  <si>
+    <t>arabiansana@yahoo.com</t>
+  </si>
+  <si>
+    <t>anees@aladwanigroup.com</t>
+  </si>
+  <si>
+    <t>raheem_ksa@hotmail.com</t>
+  </si>
+  <si>
+    <t>mnt_naveedkhan@yahoo.com</t>
+  </si>
+  <si>
+    <t>faltaameer@yahoo.com</t>
+  </si>
+  <si>
+    <t>asd__cont@hotmail.com</t>
+  </si>
+  <si>
+    <t>market@sallyhome.net</t>
+  </si>
+  <si>
+    <t>mussad_rana@yahoo.com</t>
+  </si>
+  <si>
+    <t>nqc.nazeem@yahoo.com</t>
+  </si>
+  <si>
+    <t>alshehri_est@yahoo.com</t>
+  </si>
+  <si>
+    <t>fazlu@expertindus.com</t>
+  </si>
+  <si>
+    <t>technitest@yahoo.com</t>
+  </si>
+  <si>
+    <t>asif@gulfababeel.com</t>
+  </si>
+  <si>
+    <t>ayman22481@yahoo.com</t>
+  </si>
+  <si>
+    <t>mudassir_sharief@yahoo.com</t>
+  </si>
+  <si>
+    <t>sales@humanpower.bkc.com</t>
+  </si>
+  <si>
+    <t>musifegroup@gmail.com</t>
+  </si>
+  <si>
+    <t>shaji@azizart.net</t>
+  </si>
+  <si>
+    <t>sknair@iage.biz,iageksa@gmail.com</t>
+  </si>
+  <si>
+    <t>س</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,16 +1217,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Helvetica"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -85,15 +1261,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -394,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:F748"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -402,40 +1582,3168 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A241" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A242" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A243" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A244" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A245" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A246" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A247" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A248" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A249" s="3"/>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A250" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A251" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A252" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A253" s="3"/>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A254" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A255" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A256" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A257" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A258" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A259" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A260" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A261" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A262" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A263" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A264" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A265" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A266" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A267" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A268" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A269" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A270" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A271" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A272" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A273" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A274" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A275" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A276" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A277" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A278" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A279" s="3"/>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A280" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A281" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A282" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A283" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A284" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A285" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A286" s="3"/>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A287" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A288" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A289" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A290" s="3"/>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A291" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A292" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A293" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A294" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A295" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A296" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A297" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A298" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A299" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A300" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A301" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A302" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A303" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A304" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A305" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A306" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A307" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A308" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A309" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A310" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A311" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A312" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A313" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A314" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A315" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A316" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A317" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A318" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A319" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A320" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A321" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A322" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A323" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A324" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A325" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A326" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A327" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A328" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A329" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A330" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A331" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A332" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A333" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A334" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A335" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A336" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A337" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A338" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A339" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A340" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A341" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A342" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A343" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A344" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A345" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A346" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A347" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A348" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A349" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A350" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A351" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A352" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A353" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A354" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A355" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A356" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A357" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A358" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A359" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A360" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A361" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A362" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A363" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A364" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A365" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A366" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A367" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A368" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A369" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A370" s="3"/>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A371" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A372" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A373" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A374" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A375" s="3"/>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A376" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A377" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A378" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A379" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A380" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A381" s="3"/>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A382" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A383" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A384" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A385" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A386" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A387" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A388" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A389" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A390" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A391" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A392" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A393" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A394" s="3"/>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A395" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A396" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A397" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A398" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A399" s="3"/>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A400" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A401" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A402" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A403" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A404" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A405" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A406" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A407" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A408" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A409" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A410" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A411" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A412" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A413" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A414" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A415" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A416" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A417" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A418" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A419" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A420" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A421" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A422" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A423" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A424" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A425" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A426" s="3"/>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A427" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A428" s="3"/>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A429" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A430" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A431" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A432" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A433" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A434" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A435" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A436" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A437" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A438" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A439" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A440" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A441" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A442" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A443" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A444" s="3"/>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A445" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A446" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A447" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A448" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A449" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A450" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A451" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A452" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A453" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A454" s="3"/>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A455" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A456" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A457" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A458" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A459" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A460" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A461" s="3"/>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A462" s="1"/>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A463" s="1"/>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A464" s="1"/>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A465" s="1"/>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A466" s="1"/>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A467" s="1"/>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A468" s="1"/>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A469" s="1"/>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A470" s="1"/>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A471" s="1"/>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A472" s="1"/>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A473" s="1"/>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A474" s="1"/>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A475" s="1"/>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A476" s="1"/>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A477" s="1"/>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A478" s="1"/>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A479" s="1"/>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A480" s="1"/>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A481" s="1"/>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A482" s="1"/>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A483" s="1"/>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A484" s="1"/>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A485" s="1"/>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A486" s="1"/>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A487" s="1"/>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A488" s="1"/>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A489" s="1"/>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A490" s="4"/>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A491" s="1"/>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A492" s="1"/>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A493" s="1"/>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A494" s="1"/>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A495" s="1"/>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A496" s="1"/>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A497" s="1"/>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A498" s="1"/>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A499" s="1"/>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A500" s="1"/>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A501" s="1"/>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A502" s="3"/>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A503" s="1"/>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A504" s="3"/>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A505" s="1"/>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A506" s="1"/>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A507" s="1"/>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A508" s="3"/>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A509" s="1"/>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A510" s="1"/>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A511" s="3"/>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A512" s="1"/>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A513" s="1"/>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A514" s="1"/>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A515" s="1"/>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A516" s="1"/>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A517" s="1"/>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A518" s="1"/>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A519" s="1"/>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A520" s="1"/>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A521" s="1"/>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A522" s="1"/>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A523" s="1"/>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A524" s="1"/>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A525" s="1"/>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A526" s="1"/>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A527" s="1"/>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A528" s="1"/>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A529" s="1"/>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A530" s="3"/>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A531" s="1"/>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A532" s="1"/>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A533" s="1"/>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A534" s="1"/>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A535" s="1"/>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A536" s="1"/>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A537" s="1"/>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A538" s="1"/>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A539" s="1"/>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A540" s="1"/>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A541" s="1"/>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A542" s="1"/>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A543" s="1"/>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A544" s="1"/>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A545" s="1"/>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A546" s="1"/>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A547" s="1"/>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A548" s="1"/>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A549" s="1"/>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A550" s="1"/>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A551" s="1"/>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A552" s="1"/>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A553" s="1"/>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A554" s="1"/>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A555" s="1"/>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A556" s="1"/>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A557" s="1"/>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A558" s="1"/>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A559" s="1"/>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A560" s="1"/>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A561" s="1"/>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A562" s="1"/>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A563" s="1"/>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A564" s="1"/>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A565" s="1"/>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A566" s="3"/>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A567" s="1"/>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A568" s="1"/>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A569" s="1"/>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A570" s="1"/>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A571" s="1"/>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A572" s="1"/>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A573" s="1"/>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A574" s="1"/>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A575" s="1"/>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A576" s="1"/>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A577" s="1"/>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A578" s="1"/>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A579" s="1"/>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A580" s="1"/>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A581" s="1"/>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A582" s="1"/>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A583" s="1"/>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A584" s="1"/>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A585" s="1"/>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A586" s="1"/>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A587" s="1"/>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A588" s="1"/>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A589" s="3"/>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A590" s="1"/>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A591" s="1"/>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A592" s="1"/>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A593" s="1"/>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A594" s="1"/>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A595" s="1"/>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A596" s="1"/>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A597" s="1"/>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A598" s="1"/>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A599" s="1"/>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A600" s="1"/>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A601" s="1"/>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A602" s="3"/>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A603" s="1"/>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A604" s="1"/>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A605" s="1"/>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A606" s="1"/>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A607" s="1"/>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A608" s="1"/>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A609" s="1"/>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A610" s="1"/>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A611" s="1"/>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A612" s="1"/>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A613" s="1"/>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A614" s="1"/>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A615" s="1"/>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A616" s="1"/>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A617" s="1"/>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A618" s="1"/>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A619" s="1"/>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A620" s="1"/>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A621" s="1"/>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A622" s="1"/>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A623" s="1"/>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A624" s="1"/>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A625" s="1"/>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A626" s="3"/>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A627" s="1"/>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A628" s="1"/>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A629" s="1"/>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A630" s="1"/>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A631" s="1"/>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A632" s="1"/>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A633" s="1"/>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A634" s="1"/>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A635" s="1"/>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A636" s="3"/>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A637" s="1"/>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A638" s="1"/>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A639" s="1"/>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A640" s="1"/>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A641" s="1"/>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A642" s="1"/>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A643" s="1"/>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A644" s="1"/>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A645" s="1"/>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A646" s="1"/>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A647" s="1"/>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A648" s="1"/>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A649" s="1"/>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A650" s="1"/>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A651" s="1"/>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A652" s="3"/>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A653" s="3"/>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A654" s="1"/>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A655" s="1"/>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A656" s="3"/>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A657" s="1"/>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A658" s="1"/>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A659" s="1"/>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A660" s="1"/>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A661" s="1"/>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A662" s="1"/>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A663" s="1"/>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A664" s="1"/>
+    </row>
+    <row r="665" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A665" s="1"/>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A666" s="1"/>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A667" s="1"/>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A668" s="1"/>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A669" s="1"/>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A670" s="1"/>
+    </row>
+    <row r="671" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A671" s="1"/>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A672" s="1"/>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A673" s="1"/>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A674" s="1"/>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A675" s="1"/>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A676" s="1"/>
+    </row>
+    <row r="677" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A677" s="1"/>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A678" s="1"/>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A679" s="1"/>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A680" s="1"/>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A681" s="1"/>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A682" s="3"/>
+    </row>
+    <row r="683" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A683" s="1"/>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A684" s="1"/>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A685" s="1"/>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A686" s="1"/>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A687" s="1"/>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A688" s="1"/>
+    </row>
+    <row r="689" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A689" s="1"/>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A690" s="1"/>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A691" s="1"/>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A692" s="1"/>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A693" s="1"/>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A694" s="1"/>
+    </row>
+    <row r="695" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A695" s="1"/>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A696" s="1"/>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A697" s="1"/>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A698" s="1"/>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A699" s="1"/>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A700" s="1"/>
+    </row>
+    <row r="701" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A701" s="1"/>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A702" s="1"/>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A703" s="1"/>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A704" s="1"/>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A705" s="1"/>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A706" s="1"/>
+    </row>
+    <row r="707" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A707" s="1"/>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A708" s="1"/>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A709" s="1"/>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A710" s="1"/>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A711" s="1"/>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A712" s="1"/>
+    </row>
+    <row r="713" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A713" s="1"/>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A714" s="1"/>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A715" s="1"/>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A716" s="1"/>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A717" s="1"/>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A718" s="3"/>
+    </row>
+    <row r="719" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A719" s="1"/>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A720" s="1"/>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A721" s="1"/>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A722" s="1"/>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A723" s="3"/>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A724" s="1"/>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A725" s="1"/>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A726" s="1"/>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A727" s="1"/>
+    </row>
+    <row r="728" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A728" s="1"/>
+    </row>
+    <row r="729" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A729" s="1"/>
+    </row>
+    <row r="730" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A730" s="1"/>
+    </row>
+    <row r="731" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A731" s="1"/>
+    </row>
+    <row r="732" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A732" s="1"/>
+    </row>
+    <row r="733" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A733" s="1"/>
+    </row>
+    <row r="734" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A734" s="1"/>
+    </row>
+    <row r="735" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A735" s="1"/>
+    </row>
+    <row r="736" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A736" s="1"/>
+    </row>
+    <row r="737" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A737" s="1"/>
+    </row>
+    <row r="738" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A738" s="4"/>
+    </row>
+    <row r="739" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A739" s="1"/>
+    </row>
+    <row r="740" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A740" s="1"/>
+    </row>
+    <row r="741" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A741" s="1"/>
+    </row>
+    <row r="742" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A742" s="1"/>
+    </row>
+    <row r="743" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A743" s="1"/>
+    </row>
+    <row r="744" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A744" s="1"/>
+    </row>
+    <row r="745" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A745" s="1"/>
+    </row>
+    <row r="746" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A746" s="1"/>
+    </row>
+    <row r="747" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A747" s="1"/>
+    </row>
+    <row r="748" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A748" s="1"/>
+      <c r="F748" t="s">
+        <v>393</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A241" r:id="rId1" xr:uid="{3305AD98-FA50-244F-A50F-CF119DB32E25}"/>
+    <hyperlink ref="A2" r:id="rId2" xr:uid="{D332B992-12F1-0945-AAB2-51C4A86F77CC}"/>
+    <hyperlink ref="A243" r:id="rId3" display="mailto:sales.d2@zulfi-sa.com" xr:uid="{7618239F-EF74-2944-B588-58651AB9D17A}"/>
+    <hyperlink ref="A244" r:id="rId4" display="mailto:info@gisf.com.sa" xr:uid="{88E55732-BF0A-F34A-AE52-B1B7453E3359}"/>
+    <hyperlink ref="A245" r:id="rId5" display="mailto:1U5SR.Ashaduzzaman@alruqee.com" xr:uid="{936B85B0-FC8F-3C48-9DB5-9519E4946AB7}"/>
+    <hyperlink ref="A246" r:id="rId6" display="mailto:imad.hadwan@mmm.com" xr:uid="{A18EBDAE-8CBE-7743-AFBD-38FBE2A46227}"/>
+    <hyperlink ref="A247" r:id="rId7" display="mailto:m.rasras@sghcl.com" xr:uid="{EDA39DA6-70C7-BA4B-9AAA-7810FB2BD6B9}"/>
+    <hyperlink ref="A248" r:id="rId8" display="mailto:raymond@zamilcd.com.sa" xr:uid="{AEC6864E-E2BC-7840-B305-F592E8EF5132}"/>
+    <hyperlink ref="A250" r:id="rId9" display="mailto:sales.alamgir@mctgroups.com" xr:uid="{DE7DD40D-948A-FB41-9AE3-E9207E3241C7}"/>
+    <hyperlink ref="A251" r:id="rId10" display="mailto:material@sources.com" xr:uid="{FE77D6F5-E680-D842-A548-612D8D467297}"/>
+    <hyperlink ref="A252" r:id="rId11" display="mailto:naseem@er.ahg.com.sa" xr:uid="{830289BD-001F-A446-82CF-629F08E2ECB8}"/>
+    <hyperlink ref="A254" r:id="rId12" display="mailto:moktrading@hotmail.com" xr:uid="{B1CA7831-934A-8944-983C-3331A91FB9B3}"/>
+    <hyperlink ref="A255" r:id="rId13" display="mailto:ashar@cesco-omron.com" xr:uid="{0F9F21F8-E9B5-8D44-8CED-146988DD5363}"/>
+    <hyperlink ref="A256" r:id="rId14" display="mailto:alain.saade@jas.com" xr:uid="{7F2BC34A-60B1-D84C-84DA-9DB2D8DE9EA3}"/>
+    <hyperlink ref="A257" r:id="rId15" display="mailto:jsunshinesa@gmail.com" xr:uid="{A09F6640-5897-4249-8A33-58D36C158711}"/>
+    <hyperlink ref="A258" r:id="rId16" display="mailto:imran@sabahtech.com" xr:uid="{7ACA7BDC-0F68-934A-BA49-C41E735C59FB}"/>
+    <hyperlink ref="A259" r:id="rId17" display="mailto:charbeljarjour@icjubail.com.sa" xr:uid="{7BA500EB-A8AF-4049-A743-E20328E7E270}"/>
+    <hyperlink ref="A260" r:id="rId18" display="mailto:khan@immh.co" xr:uid="{68A1D7A4-5399-414E-97C0-7DD9557E4E6E}"/>
+    <hyperlink ref="A261" r:id="rId19" display="mailto:info@assawayer.com/palaksha@assawayer.com" xr:uid="{6B791C2A-F4A3-3D42-AFF8-72A059DD8A1E}"/>
+    <hyperlink ref="A262" r:id="rId20" display="mailto:manoj.kumar@almojilservices.com" xr:uid="{5AA21E6F-27FB-8A4C-917F-AA6F4544C608}"/>
+    <hyperlink ref="A263" r:id="rId21" display="mailto:info@miesteel.com" xr:uid="{992B345C-8ABD-564E-B81E-F7D26504DCC1}"/>
+    <hyperlink ref="A264" r:id="rId22" display="mailto:sales.jubail@alkhodartravel.com" xr:uid="{77785FF1-A5F9-BD45-9274-EFD4FE92B81C}"/>
+    <hyperlink ref="A265" r:id="rId23" display="mailto:1ucsr.Ashaduzzaman@alruqee.com" xr:uid="{D5C79CDE-04B5-E749-B836-8BF1EF7E7211}"/>
+    <hyperlink ref="A266" r:id="rId24" display="mailto:info@aladwanigroup.com" xr:uid="{96384385-C8B5-6340-8412-819312717A42}"/>
+    <hyperlink ref="A267" r:id="rId25" display="mailto:trezk@elajougroup.com" xr:uid="{03D30324-E65A-8E42-98DA-79DE1551DEB5}"/>
+    <hyperlink ref="A268" r:id="rId26" display="mailto:maraicar.s@worklogixme.com" xr:uid="{A8D6D68A-C1EF-B842-91CB-AA2166089167}"/>
+    <hyperlink ref="A269" r:id="rId27" display="mailto:ksbiju@rashidaldossary.com" xr:uid="{F37D8D8C-CA67-214B-901E-DB0BC934E77A}"/>
+    <hyperlink ref="A270" r:id="rId28" display="mailto:info@inmaajubail.com" xr:uid="{4066BDF4-C6E9-FA41-808E-E661B0D61B6C}"/>
+    <hyperlink ref="A271" r:id="rId29" display="mailto:alg@alf-fouzangroup.com" xr:uid="{2872BD39-C3BC-E742-B71B-BAADD5A93CFA}"/>
+    <hyperlink ref="A272" r:id="rId30" display="mailto:masudcac@gmail.com" xr:uid="{B84AC0B8-24E0-CF42-8C6E-160C818DDBC7}"/>
+    <hyperlink ref="A273" r:id="rId31" display="mailto:usman@aladwanigroup.com" xr:uid="{24AAD7ED-B105-1642-AF31-3DE7EE3DC46F}"/>
+    <hyperlink ref="A274" r:id="rId32" display="mailto:asif.malik@nabharubber.com" xr:uid="{42104EFC-6DBF-2E41-8391-52B35BEB8EFB}"/>
+    <hyperlink ref="A275" r:id="rId33" display="mailto:a.hajiri@developmentsources.org" xr:uid="{E3A1EFBD-EBF1-7543-A3B0-1565D27AE748}"/>
+    <hyperlink ref="A276" r:id="rId34" display="mailto:1u4sales.Azeemuddin@alruqee.com" xr:uid="{35A4A701-29CD-984E-923D-CD80CDD568BA}"/>
+    <hyperlink ref="A277" r:id="rId35" display="mailto:hadi_alajmi2013@yahoo.com" xr:uid="{1EDAB813-2A0F-044F-9376-23FF2491482F}"/>
+    <hyperlink ref="A278" r:id="rId36" display="mailto:abdulrahman.aggad@inmatrading.com.sa" xr:uid="{6D73310F-EF46-1847-A98A-EDCF8EC99088}"/>
+    <hyperlink ref="A280" r:id="rId37" display="mailto:info@altamayz.com" xr:uid="{3BE930BE-FB1B-924E-BE68-519D3CE8FD9D}"/>
+    <hyperlink ref="A281" r:id="rId38" display="mailto:info@hatcogroups.com" xr:uid="{BF39ECD0-FFAE-1145-9D22-BDFF8BD9B7CF}"/>
+    <hyperlink ref="A282" r:id="rId39" display="mailto:ibashir@sahara.com" xr:uid="{99E659A0-20FF-944C-94CD-E81FDC07ACAA}"/>
+    <hyperlink ref="A283" r:id="rId40" display="mailto:aee_jubail@arabequipmentest.com" xr:uid="{1444DAEC-4A63-BB42-88AE-3A5EE33DB6C0}"/>
+    <hyperlink ref="A284" r:id="rId41" display="mailto:rgupta@idexcorp.com" xr:uid="{45F33938-1236-4B49-AF90-B4BFE4C156D8}"/>
+    <hyperlink ref="A285" r:id="rId42" display="mailto:fahadtnr@aloctg.com" xr:uid="{6DB2BE0D-61D2-3048-A81C-566EC313989B}"/>
+    <hyperlink ref="A287" r:id="rId43" display="mailto:info@makana.com.sa" xr:uid="{66A8A4C7-85AA-ED4F-A612-485841B44ADB}"/>
+    <hyperlink ref="A288" r:id="rId44" display="mailto:omer@advancemachinery.com.sa" xr:uid="{FAB0E87A-B44E-8549-B3C7-A93A539CD3DF}"/>
+    <hyperlink ref="A289" r:id="rId45" display="mailto:planning@algaswa.com" xr:uid="{60C281E7-200B-F341-8EFA-51CEC632E3A5}"/>
+    <hyperlink ref="A291" r:id="rId46" display="mailto:info@altamyaz.com" xr:uid="{928C562B-40D9-A546-A35B-5E3FCE2E8E16}"/>
+    <hyperlink ref="A292" r:id="rId47" display="mailto:almhannaacostruction@gmail.com" xr:uid="{B15DE487-2F12-2E40-B6DB-3BB065FEA576}"/>
+    <hyperlink ref="A293" r:id="rId48" display="mailto:abhilash@jbg.sa.com" xr:uid="{28B62A34-1AA6-8D49-B79E-72F8B8A2E2E1}"/>
+    <hyperlink ref="A294" r:id="rId49" display="mailto:allafinri@yahoo.com" xr:uid="{BD70C5B9-2C39-994A-B930-E5880B61C117}"/>
+    <hyperlink ref="A295" r:id="rId50" display="mailto:tharwt_saudirod@yahoo.com" xr:uid="{BEFB09C4-7E13-0948-BE1C-583FD27683A3}"/>
+    <hyperlink ref="A296" r:id="rId51" display="mailto:arshad@qurumtech.com" xr:uid="{6EB48AAC-2361-DD47-9A94-0BE68C650ED2}"/>
+    <hyperlink ref="A297" r:id="rId52" display="mailto:rhejubail@jeraisy.com" xr:uid="{51540377-BE56-1D49-A6FE-D6795BB78FD4}"/>
+    <hyperlink ref="A298" r:id="rId53" display="mailto:16HMA.Aftab@alruqee.com" xr:uid="{AE648564-B504-F245-B323-BAC525459C70}"/>
+    <hyperlink ref="A299" r:id="rId54" display="mailto:emetals@alfozan.com" xr:uid="{91D9BB9F-E97D-8A4A-B283-D3B6D916352E}"/>
+    <hyperlink ref="A300" r:id="rId55" display="mailto:sashidharan1949@yahoo.com" xr:uid="{CC2B5DBB-B747-9645-AE0D-99A7D7D7136C}"/>
+    <hyperlink ref="A301" r:id="rId56" display="mailto:tshanavas@aaltaher.com" xr:uid="{36BD2F2F-B637-CD47-9902-CDDE73A5B10D}"/>
+    <hyperlink ref="A302" r:id="rId57" display="mailto:jamal@firetechksa.com" xr:uid="{E9523AD8-85DC-0948-B512-A0100BBDA978}"/>
+    <hyperlink ref="A303" r:id="rId58" display="mailto:sreekanth.p@pressuresystemsksa.com" xr:uid="{099B13F1-C508-3E4F-8A1A-254F4F68350E}"/>
+    <hyperlink ref="A304" r:id="rId59" display="mailto:creditcontrol.Ashaduzzaman@alruqee.com" xr:uid="{0DA23544-DFDD-954D-881A-ADB1AE5414C1}"/>
+    <hyperlink ref="A305" r:id="rId60" display="mailto:majid@arabianlojam.com" xr:uid="{89BFBDE7-62D6-0641-B956-488691C12D09}"/>
+    <hyperlink ref="A306" r:id="rId61" display="mailto:craneservices@smart.arabian.com" xr:uid="{216038F6-1B86-F348-899E-E459F938FB65}"/>
+    <hyperlink ref="A307" r:id="rId62" display="mailto:burgeon.it@gmail.com" xr:uid="{A5144964-0A04-D640-B7F3-9930AFC25D32}"/>
+    <hyperlink ref="A308" r:id="rId63" display="mailto:alshakra-hassnain@hotmail.com" xr:uid="{9EEFC045-BCB6-7A4D-9141-07321B34D28F}"/>
+    <hyperlink ref="A309" r:id="rId64" display="mailto:ameen_aso@yahoo.com" xr:uid="{FBFE5C23-8A01-6E47-907A-E0BEE7285239}"/>
+    <hyperlink ref="A310" r:id="rId65" display="mailto:ialmulla@emc.com.sa" xr:uid="{4543CD4A-47AA-6245-8831-77C02B86F1B1}"/>
+    <hyperlink ref="A311" r:id="rId66" display="mailto:moktrading@hotmail.com" xr:uid="{69706408-B69A-024E-8F05-47CD0008AB55}"/>
+    <hyperlink ref="A312" r:id="rId67" display="mailto:burpowerliftersa.comhan@" xr:uid="{8CEA63B7-4B78-F642-A162-CFD5BB0135EC}"/>
+    <hyperlink ref="A313" r:id="rId68" display="mailto:kashif.masood@arabianetimaad.com" xr:uid="{0B6743B7-76B4-4F45-9543-6FC69BF2E2D5}"/>
+    <hyperlink ref="A314" r:id="rId69" display="mailto:hadi_alajmi2013@yahoo.com" xr:uid="{E61F5796-4265-5B4F-A8C6-A0BB28B49869}"/>
+    <hyperlink ref="A315" r:id="rId70" display="mailto:zakir.rental@gmail.com" xr:uid="{6AC5749E-9218-A74F-8FD4-6E0C39A3A15B}"/>
+    <hyperlink ref="A316" r:id="rId71" display="mailto:dawood@silverlineassociates.com" xr:uid="{563F2BB6-F16E-6041-B7E6-95C5A07B6957}"/>
+    <hyperlink ref="A317" r:id="rId72" display="mailto:ac@bdrdm.com" xr:uid="{BDCC1163-6FA2-2940-A482-B9B84281240E}"/>
+    <hyperlink ref="A318" r:id="rId73" display="mailto:teamlifting@gmail.com" xr:uid="{087B38D5-C845-DA44-8482-9EF2590F7A5F}"/>
+    <hyperlink ref="A319" r:id="rId74" display="mailto:jhun.ts@gulfchanels.com" xr:uid="{706BFFF3-FF21-9242-B6B0-5552EECE198F}"/>
+    <hyperlink ref="A320" r:id="rId75" display="mailto:ismail.alalwan@gmail.com" xr:uid="{A31925D5-6BC1-1B42-9CA0-7D7243C3D123}"/>
+    <hyperlink ref="A321" r:id="rId76" display="mailto:omprakash@pangulfws.com" xr:uid="{CFAF9C37-66EF-D14E-95A1-A1DD906012CF}"/>
+    <hyperlink ref="A322" r:id="rId77" display="mailto:ibashir@sahara.com" xr:uid="{2432024A-8E95-CE46-A2BE-F74A786BA1F2}"/>
+    <hyperlink ref="A323" r:id="rId78" display="mailto:siddique@hicksa.com" xr:uid="{29B250F9-7C34-6A45-8EAA-9C047A0C25AE}"/>
+    <hyperlink ref="A324" r:id="rId79" display="mailto:munazzah.shariq@alkhodari.com" xr:uid="{A63CFDB1-4D38-1F43-9AEE-87D7FDE23CFB}"/>
+    <hyperlink ref="A325" r:id="rId80" display="mailto:nathaniel@intecc.co" xr:uid="{F16074B0-FB6F-1445-8274-E70EFE8AC229}"/>
+    <hyperlink ref="A326" r:id="rId81" display="mailto:threedimension1@yahoo.com" xr:uid="{47D74502-0C08-EA48-BC79-76CB5EEA1C1D}"/>
+    <hyperlink ref="A327" r:id="rId82" display="mailto:kkumar@supportarabia.com" xr:uid="{A91568B9-C54C-2946-A060-1A75916C57F6}"/>
+    <hyperlink ref="A328" r:id="rId83" display="mailto:rajan@misarabia.com.sa" xr:uid="{7E386E66-35D5-C24C-9AE2-463B86D78809}"/>
+    <hyperlink ref="A329" r:id="rId84" display="mailto:townhardware@gmail.com" xr:uid="{A939E705-A325-B14D-943F-60306F8CEBB1}"/>
+    <hyperlink ref="A330" r:id="rId85" display="mailto:sales@sharpgt.com" xr:uid="{547950EF-A08C-9246-BEE5-08EC78ABC412}"/>
+    <hyperlink ref="A331" r:id="rId86" display="mailto:ahmed.ahmed@aramex.com" xr:uid="{67BA957A-3BF2-9D4A-B4B2-6707F9CCFBEA}"/>
+    <hyperlink ref="A332" r:id="rId87" display="mailto:john@misarabia.com.sa" xr:uid="{73DF1FED-EBC5-554D-97A9-129E214A022B}"/>
+    <hyperlink ref="A333" r:id="rId88" display="mailto:vasanth@ferrograte.com" xr:uid="{F80A1177-4A92-E945-87FA-AB45B294A5C7}"/>
+    <hyperlink ref="A334" r:id="rId89" display="mailto:reemtrading12@yahoo.com" xr:uid="{8881E896-FC4B-744D-BA5E-C30571E51B72}"/>
+    <hyperlink ref="A335" r:id="rId90" display="mailto:info@rkest.com" xr:uid="{7240BD56-63A9-F446-A8AC-5786A5E77557}"/>
+    <hyperlink ref="A336" r:id="rId91" display="mailto:hithesh@mister-machine.com" xr:uid="{0DBBD67E-C11F-5A4F-A459-40ED727DCBBC}"/>
+    <hyperlink ref="A337" r:id="rId92" display="mailto:njm.sah@gmail.com" xr:uid="{091AA833-A2F7-544A-BD81-E28F77495725}"/>
+    <hyperlink ref="A338" r:id="rId93" display="mailto:merajnafco.jnsf@gmail.com" xr:uid="{DE9EDE67-E0FE-A14E-854B-FAEFA33BD7F8}"/>
+    <hyperlink ref="A339" r:id="rId94" display="mailto:jbsales@sste.sa.com" xr:uid="{8EE30D8D-D230-6242-95B2-DDA2A569F66B}"/>
+    <hyperlink ref="A340" r:id="rId95" display="mailto:gamarabiasm@gmail.com" xr:uid="{77D00205-233D-F945-A429-55243C03A242}"/>
+    <hyperlink ref="A341" r:id="rId96" display="mailto:afsal@dayalsteelonline.com" xr:uid="{6BDA1A7A-8E4A-9046-ABF3-C8CDD99F46BA}"/>
+    <hyperlink ref="A342" r:id="rId97" display="mailto:emetals@alfozan.com" xr:uid="{6FEDBF6B-ABF8-154B-BCD9-5E3AE279D1F8}"/>
+    <hyperlink ref="A343" r:id="rId98" display="mailto:akif@dli-it.com" xr:uid="{30F05D75-F78D-E049-A551-4518701CA25D}"/>
+    <hyperlink ref="A344" r:id="rId99" display="mailto:zhmalik20710@gmail.com" xr:uid="{E3B975F3-489D-3D44-B61D-6AD81B9691C5}"/>
+    <hyperlink ref="A345" r:id="rId100" display="mailto:shameer@scomsys.com" xr:uid="{75A91844-1011-DA4D-BCF7-E8E77F24A505}"/>
+    <hyperlink ref="A346" r:id="rId101" display="mailto:4E2CSR.JOSE@alruqee.com" xr:uid="{4F47AEF6-ADEC-DA42-8339-4FFD8C02D092}"/>
+    <hyperlink ref="A347" r:id="rId102" display="mailto:aliabdel@univest,com.sa" xr:uid="{0CACFDB6-9ADD-2D4D-B1CB-305AEB0EC43F}"/>
+    <hyperlink ref="A348" r:id="rId103" display="mailto:CONTACT@SAUINTGROUP.COM" xr:uid="{F5E753EB-7636-DA4D-A41F-0E26F34407ED}"/>
+    <hyperlink ref="A349" r:id="rId104" display="mailto:wabduljabbar@alkhorayef.com" xr:uid="{9D9AD0BD-CFCE-4249-9C04-DC6C3DEBC074}"/>
+    <hyperlink ref="A350" r:id="rId105" display="mailto:info@jag.com.sa" xr:uid="{8CB13423-195A-2848-80A2-BE8ECEA62BFB}"/>
+    <hyperlink ref="A351" r:id="rId106" display="mailto:asmahamood@gmail.com" xr:uid="{B73D583C-3EA4-8946-97BB-4C1E615AACB0}"/>
+    <hyperlink ref="A352" r:id="rId107" display="mailto:alwaha-ksa@hotmail.com" xr:uid="{624C6580-B408-CE47-B593-9274979E28C8}"/>
+    <hyperlink ref="A353" r:id="rId108" display="mailto:faisal@gisf.com.sa" xr:uid="{6FB77C76-9A23-6744-BDED-FF552B5C16F0}"/>
+    <hyperlink ref="A354" r:id="rId109" display="mailto:sales.ati@ati-gulf.com" xr:uid="{61BDBBE5-8731-B845-B792-D4CFC0A9CDB4}"/>
+    <hyperlink ref="A355" r:id="rId110" display="mailto:mubin@psime.com" xr:uid="{4242BA3C-F0E4-934D-B070-B8C14AA47FD8}"/>
+    <hyperlink ref="A357" r:id="rId111" display="mailto:intekhab@hhaulers.com" xr:uid="{5532C93D-2C8C-2B4E-A02D-106A49BE3C32}"/>
+    <hyperlink ref="A358" r:id="rId112" display="mailto:info@altamyaz.com" xr:uid="{C969A0E6-F1C0-DD4E-A86C-A1D507B8F0A8}"/>
+    <hyperlink ref="A359" r:id="rId113" display="mailto:mansoor0501193790@gmail.com" xr:uid="{0379169B-D902-D94F-B174-1935B8EA6903}"/>
+    <hyperlink ref="A360" r:id="rId114" display="mailto:iqbal@anseglobal.com" xr:uid="{FD8426C6-D33E-0148-91B9-43073908B2DA}"/>
+    <hyperlink ref="A361" r:id="rId115" display="mailto:sales-saudi@vineyardgroup.net" xr:uid="{42916EF7-08AC-6341-B6E1-6F5BDF3A5FF1}"/>
+    <hyperlink ref="A362" r:id="rId116" display="mailto:afsal@dayalsteelonline.com" xr:uid="{58E47130-EEB0-A440-B7A4-F575D2F6086A}"/>
+    <hyperlink ref="A363" r:id="rId117" display="mailto:shibith@aladwanigroup.com" xr:uid="{E63F233B-D7DB-0C46-A590-90559CF7FFE5}"/>
+    <hyperlink ref="A364" r:id="rId118" display="mailto:sales@fatehaljubail.com" xr:uid="{61133D4D-38E1-B64F-B858-5C2C6C512352}"/>
+    <hyperlink ref="A365" r:id="rId119" display="mailto:aee_jubail@arabequipmentest.com" xr:uid="{B2CCC7A4-7C5E-2C44-89ED-883FD20E0873}"/>
+    <hyperlink ref="A366" r:id="rId120" display="mailto:mke@technotogroup.com" xr:uid="{403C7818-B6A1-AA43-96F7-A16FC04245FB}"/>
+    <hyperlink ref="A367" r:id="rId121" display="mailto:sajad@madeenapvc.com" xr:uid="{7F5156E5-97FB-0E44-AF30-E66A23576814}"/>
+    <hyperlink ref="A368" r:id="rId122" display="mailto:jubail@namat.com" xr:uid="{99AC467F-7117-F044-8ACE-F49CBC89A2F6}"/>
+    <hyperlink ref="A369" r:id="rId123" display="mailto:jubaillshrm@mejdaf.com" xr:uid="{B057F5CD-7CCF-624A-84AD-981EDEB5294A}"/>
+    <hyperlink ref="A371" r:id="rId124" display="mailto:info@alshamranigroup.com" xr:uid="{9BF834F3-5904-2245-AF28-6891B3772FDB}"/>
+    <hyperlink ref="A372" r:id="rId125" display="mailto:geogrid@latifia.com" xr:uid="{904BF06C-5602-CC45-BAEC-86E5B5293CF7}"/>
+    <hyperlink ref="A373" r:id="rId126" display="mailto:fabco@salembathamer.com" xr:uid="{EB0530BB-6BCC-394C-81AB-1FC6B3FA72EB}"/>
+    <hyperlink ref="A374" r:id="rId127" display="mailto:taha@aktesa.com" xr:uid="{DD3E12E7-21A6-CE4D-9286-BF434B4389AB}"/>
+    <hyperlink ref="A376" r:id="rId128" display="mailto:mohammed.elshaarawy@el-sewedy.com" xr:uid="{4AE2BCDD-F29E-9542-B4C5-8C7401BB3602}"/>
+    <hyperlink ref="A377" r:id="rId129" display="mailto:ros5753322@hotmail.com" xr:uid="{50DFF51B-B603-F541-B88D-F97B05D3E1FB}"/>
+    <hyperlink ref="A378" r:id="rId130" display="mailto:haitham@almousasacables.com" xr:uid="{3B1AEA04-5085-BF45-817D-46A9400B63C7}"/>
+    <hyperlink ref="A379" r:id="rId131" display="mailto:hadippress@yahoo.com" xr:uid="{9AD06712-0F8D-B84A-BD56-E73F339186A0}"/>
+    <hyperlink ref="A380" r:id="rId132" display="mailto:omarna@akh.com.sa" xr:uid="{A76B25E9-7BCC-6B48-A91E-54AB21BFB6B0}"/>
+    <hyperlink ref="A382" r:id="rId133" display="mailto:info@eaglehydraulicservice.com" xr:uid="{7E20394B-1C1F-C44C-AAA8-F1C02D6EFA2F}"/>
+    <hyperlink ref="A383" r:id="rId134" display="mailto:fabco@salembathamer.com" xr:uid="{53B8C60B-D321-5C4F-B434-8C2B31039BDF}"/>
+    <hyperlink ref="A384" r:id="rId135" display="mailto:aee_jubail@arabequipmentest.com" xr:uid="{53A383F9-4A2B-1346-BA41-DB55A8BCAF8E}"/>
+    <hyperlink ref="A385" r:id="rId136" display="mailto:koshy@khamisainhardware.com" xr:uid="{9F5C763B-47E5-A34E-BF29-2380C67B8139}"/>
+    <hyperlink ref="A386" r:id="rId137" display="mailto:info@saudithalate.com" xr:uid="{0147EA26-4B2F-B74E-BF27-8F189323A263}"/>
+    <hyperlink ref="A387" r:id="rId138" display="mailto:fabco@salembathamer.com" xr:uid="{774D451B-90D6-E542-9DCC-5D2637B60DF7}"/>
+    <hyperlink ref="A388" r:id="rId139" display="mailto:sales@hindasent.com" xr:uid="{8B105DB4-D468-6545-9814-E6ABCA015A19}"/>
+    <hyperlink ref="A389" r:id="rId140" display="mailto:sheikh_ngc@yahoo.com" xr:uid="{C02C4964-080F-4F44-858B-9A3ABA7D2C16}"/>
+    <hyperlink ref="A390" r:id="rId141" display="mailto:allafinri@yahoo.com" xr:uid="{6CD4C2EF-092D-2249-8712-E585AD7BE07B}"/>
+    <hyperlink ref="A391" r:id="rId142" display="mailto:liyaqat_m@yahoo.com" xr:uid="{E0933FAD-2B56-6A41-BD65-B3D1BEB6CC0C}"/>
+    <hyperlink ref="A392" r:id="rId143" display="mailto:hertz@alkhodari.com" xr:uid="{98E4C47B-3E4E-0F46-AF43-FD039A507683}"/>
+    <hyperlink ref="A393" r:id="rId144" display="mailto:mha_mangalore@yahoo.com" xr:uid="{80FDB944-8DB5-964F-B1A2-868B67E4C080}"/>
+    <hyperlink ref="A395" r:id="rId145" display="mailto:sukeshcrystal@yahoo.com" xr:uid="{47943ADB-D60D-7347-9452-F45FBD7BC05E}"/>
+    <hyperlink ref="A396" r:id="rId146" display="mailto:samaajubail@gmail.com" xr:uid="{37089C86-9A21-4049-BCDA-D291B26B414F}"/>
+    <hyperlink ref="A397" r:id="rId147" display="mailto:info@superior.com.sa" xr:uid="{0629062D-12CC-E540-9085-34FBBB8E0390}"/>
+    <hyperlink ref="A398" r:id="rId148" display="mailto:info@enzonme.com" xr:uid="{68093698-6395-0740-B59E-BD3512F77716}"/>
+    <hyperlink ref="A400" r:id="rId149" display="mailto:mbmjubail@yahoo.com" xr:uid="{90C0C5CF-1F70-6847-988A-7688BCC4E514}"/>
+    <hyperlink ref="A401" r:id="rId150" display="mailto:ith@ithest.net" xr:uid="{D70C7402-B245-E348-9713-A6CEA52C21F4}"/>
+    <hyperlink ref="A402" r:id="rId151" display="mailto:sheikh_ngc@yahoo.com" xr:uid="{DBB6BC13-00E9-1D4F-A3D1-BFDF72B6D0E2}"/>
+    <hyperlink ref="A403" r:id="rId152" display="mailto:pillai_us1@yahoo.com" xr:uid="{16914A8F-B03D-E344-AE03-3C5D5A54839E}"/>
+    <hyperlink ref="A404" r:id="rId153" display="mailto:dastagir@cmci-sa.com" xr:uid="{B72132D7-276C-EF41-B6ED-3028C9602F1D}"/>
+    <hyperlink ref="A405" r:id="rId154" display="mailto:info@eaglehydraulicservice.com" xr:uid="{5AAA492D-0D58-214C-98A6-867C1B781206}"/>
+    <hyperlink ref="A406" r:id="rId155" display="mailto:fiazsiddique@yahoo.com" xr:uid="{E06DE09B-CE62-B14E-B056-F2129A10D67B}"/>
+    <hyperlink ref="A407" r:id="rId156" display="mailto:sales@alhodaco.com" xr:uid="{BA254814-944C-544B-BFC4-3230043ECDD1}"/>
+    <hyperlink ref="A408" r:id="rId157" display="mailto:info@atc.sa.com" xr:uid="{24B42EFF-BDDB-1945-860A-A1F4CE4A85C3}"/>
+    <hyperlink ref="A409" r:id="rId158" display="mailto:daniel.thomson@worleypersons.com" xr:uid="{33636F51-2C46-E141-A6E6-C9A069DC81C3}"/>
+    <hyperlink ref="A410" r:id="rId159" display="mailto:salim.moideen@aramco.com" xr:uid="{A4226D30-A41A-CC42-9A4A-C31A59FBCEA2}"/>
+    <hyperlink ref="A411" r:id="rId160" display="mailto:khaled-thiab@yahoo.com" xr:uid="{E876D917-2361-AF42-BAFD-012F363721DE}"/>
+    <hyperlink ref="A412" r:id="rId161" display="mailto:%23J-R-G-C@Hotmail.com" xr:uid="{86142651-B521-0E40-A4F9-2071464FCFF2}"/>
+    <hyperlink ref="A413" r:id="rId162" display="mailto:bijisnairamasco@gmail.com" xr:uid="{AFC74605-95E5-5E40-ABBC-4888C79185C1}"/>
+    <hyperlink ref="A414" r:id="rId163" display="mailto:sufyan@sste,sa.com" xr:uid="{EE9FBAC3-9FA5-F54A-A1E2-69D235A1DF66}"/>
+    <hyperlink ref="A415" r:id="rId164" display="mailto:az_mod2009@yahoo.com" xr:uid="{AB77BFDA-9CD7-7D46-8773-C23199A85599}"/>
+    <hyperlink ref="A416" r:id="rId165" display="mailto:ajmi-130@hotmail.com" xr:uid="{3D271F83-133E-EF48-B378-9C067F70ED1F}"/>
+    <hyperlink ref="A417" r:id="rId166" display="mailto:fahad.mic@gmail.com" xr:uid="{4950F872-6187-9E45-B7FE-F29E56D74DD0}"/>
+    <hyperlink ref="A418" r:id="rId167" display="mailto:contracts@alliedtechsa.com" xr:uid="{341AF04C-D0BE-A049-9B9E-7FE7917FB0BD}"/>
+    <hyperlink ref="A419" r:id="rId168" display="mailto:biju@southemrock.com.sa" xr:uid="{A54A5233-8481-0E4D-9178-4A0942B9BBAC}"/>
+    <hyperlink ref="A420" r:id="rId169" display="mailto:shajik@awtads.com" xr:uid="{4EDC87F6-BEC5-FB42-8507-2ABE46CECBC1}"/>
+    <hyperlink ref="A421" r:id="rId170" display="mailto:mki_akhas@yahoo.com" xr:uid="{DC02679F-069F-DF45-98B6-2D9AEE0DC704}"/>
+    <hyperlink ref="A422" r:id="rId171" display="mailto:eliteinvention@gmail.com" xr:uid="{5CBBABC7-5132-F241-B769-DF80298BA3F1}"/>
+    <hyperlink ref="A423" r:id="rId172" display="mailto:zaki_dksc@yahoo.com" xr:uid="{64B0FE3F-1E84-2C43-A2DF-084B03F34BBE}"/>
+    <hyperlink ref="A424" r:id="rId173" display="mailto:johir_kondaker@yahoo.com" xr:uid="{83D259EB-4ED1-6344-9216-5DE248C39BBC}"/>
+    <hyperlink ref="A425" r:id="rId174" display="mailto:amamon@gulfconnectsa.com" xr:uid="{3FCDB7D2-975A-F649-B299-FDE21D9DD218}"/>
+    <hyperlink ref="A427" r:id="rId175" display="mailto:alm_almgir@yahoo.com" xr:uid="{B867B413-BE6F-664B-B36B-88BC7035C7D6}"/>
+    <hyperlink ref="A429" r:id="rId176" display="mailto:unitedaseel@gmail.com" xr:uid="{6581D803-6D42-9F4C-8444-8FE8DF279A40}"/>
+    <hyperlink ref="A430" r:id="rId177" display="mailto:raslkhaleej2020@yahoo.com" xr:uid="{569D9EBC-B200-BD40-A405-60B189448391}"/>
+    <hyperlink ref="A431" r:id="rId178" display="mailto:navasteejan@gmail.com" xr:uid="{2A9F24D1-B343-FC44-A5B4-D12D6FF842EE}"/>
+    <hyperlink ref="A432" r:id="rId179" display="mailto:fahad_khalid01@yahoo.com" xr:uid="{DF2267B2-4276-0240-8DBF-61CAD47D9372}"/>
+    <hyperlink ref="A433" r:id="rId180" display="mailto:unitedaseel@gmail.com" xr:uid="{86F322B3-9B4D-C944-B02C-ABBE834B3689}"/>
+    <hyperlink ref="A434" r:id="rId181" display="mailto:mujibkavitvr@yahoo.co.in" xr:uid="{6D828132-45AA-574D-9B58-D7544916BF91}"/>
+    <hyperlink ref="A435" r:id="rId182" display="mailto:msquarebabu_mrb@yahoo.com" xr:uid="{E219FD3A-CCB3-704C-AA71-03D3AEE87244}"/>
+    <hyperlink ref="A436" r:id="rId183" display="mailto:mahacodmm@yahoo.com" xr:uid="{A89822B0-B674-5743-8297-DBDADC922341}"/>
+    <hyperlink ref="A437" r:id="rId184" display="mailto:jsgce2009@yahoo.com" xr:uid="{10D1EECA-04AC-F440-8475-D90154B25D0F}"/>
+    <hyperlink ref="A438" r:id="rId185" display="mailto:arabiansana@yahoo.com" xr:uid="{68EAE234-8770-9C45-8408-3EB22EDF5E2D}"/>
+    <hyperlink ref="A439" r:id="rId186" display="mailto:anees@aladwanigroup.com" xr:uid="{A3AEEE77-B87B-B044-9658-08F081FEE43D}"/>
+    <hyperlink ref="A440" r:id="rId187" display="mailto:raheem_ksa@hotmail.com" xr:uid="{775FD0BD-8CD3-9D43-BC48-C10AF092E090}"/>
+    <hyperlink ref="A441" r:id="rId188" display="mailto:mnt_naveedkhan@yahoo.com" xr:uid="{01AB8AF9-3C9F-E54F-80C7-0EC079829E76}"/>
+    <hyperlink ref="A442" r:id="rId189" display="mailto:faltaameer@yahoo.com" xr:uid="{5F286F19-FE05-D844-83F0-D4426AE18433}"/>
+    <hyperlink ref="A443" r:id="rId190" display="mailto:asd__cont@hotmail.com" xr:uid="{1FEC497E-EAC9-E048-BEC4-CD6565E0CD0E}"/>
+    <hyperlink ref="A445" r:id="rId191" display="mailto:fahad_khalid01@yahoo.com" xr:uid="{14E0C6EB-B37A-7E46-AA94-DAFBE3450DE5}"/>
+    <hyperlink ref="A446" r:id="rId192" display="mailto:market@sallyhome.net" xr:uid="{1DE022CC-A8B8-4C4A-B82A-EAD6C412B4CD}"/>
+    <hyperlink ref="A447" r:id="rId193" display="mailto:raslkhaleej2020@yahoo.com" xr:uid="{F9602561-642C-6740-9592-5D349F0F788E}"/>
+    <hyperlink ref="A448" r:id="rId194" display="mailto:mussad_rana@yahoo.com" xr:uid="{E141EEB2-F98C-C345-A0A7-AB23D73983BD}"/>
+    <hyperlink ref="A449" r:id="rId195" display="mailto:nqc.nazeem@yahoo.com" xr:uid="{5BD57E0A-F4D9-384A-ACB2-6A9AEA132E72}"/>
+    <hyperlink ref="A450" r:id="rId196" display="mailto:alshehri_est@yahoo.com" xr:uid="{5CFE9DAF-31C6-5742-BB21-F688E439BFF3}"/>
+    <hyperlink ref="A451" r:id="rId197" display="mailto:fazlu@expertindus.com" xr:uid="{25745E21-060D-F741-B75A-AD8E5526BDB6}"/>
+    <hyperlink ref="A452" r:id="rId198" display="mailto:technitest@yahoo.com" xr:uid="{EDC28B25-5229-2949-86F2-F7F389F503DF}"/>
+    <hyperlink ref="A453" r:id="rId199" display="mailto:asif@gulfababeel.com" xr:uid="{D3C8CD54-2172-834A-9A62-71156681DFE5}"/>
+    <hyperlink ref="A455" r:id="rId200" display="mailto:ayman22481@yahoo.com" xr:uid="{BF0C1706-2749-8D4B-A46E-1004E1DA0660}"/>
+    <hyperlink ref="A456" r:id="rId201" display="mailto:mudassir_sharief@yahoo.com" xr:uid="{299C328F-64C2-4744-B807-6E1FD9DF3074}"/>
+    <hyperlink ref="A457" r:id="rId202" display="mailto:sales@humanpower.bkc.com" xr:uid="{341E81AF-D893-0E44-BFA7-E9C229A3EAF5}"/>
+    <hyperlink ref="A458" r:id="rId203" display="mailto:musifegroup@gmail.com" xr:uid="{487766F6-B8A0-484F-B84C-CD1500104309}"/>
+    <hyperlink ref="A459" r:id="rId204" display="mailto:shaji@azizart.net" xr:uid="{BF42825B-62C8-AF4D-ACA9-73F44849F817}"/>
+    <hyperlink ref="A460" r:id="rId205" display="mailto:sknair@iage.biz,iageksa@gmail.com" xr:uid="{D9018B80-9E97-6D4B-958E-788E99A76C1C}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>